--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_003/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_003/extracted.xlsx
@@ -485,6 +485,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -685,11 +690,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -725,11 +725,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -761,6 +756,11 @@
       </text>
     </comment>
     <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1126,6 +1126,11 @@
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1403,17 +1408,17 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Pump 250 CFD Q-H and NPSH Prediction</t>
+          <t>Centrifugal Pump CFD Q–H and NPSH Prediction</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>CFD prediction of Q-H curve, shaft torque, BEP efficiency, volute tongue pressure pulsation, and NPSHr for a 250 mm end-suction centrifugal pump at 1750 rpm</t>
+          <t>CFD prediction of Q–H curve, torque, BEP, and NPSHr for a 250 mm single-stage centrifugal pump at 1750 rpm</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>Steady-state (MRF frozen-rotor) and transient (sliding-mesh) RANS CFD using ANSYS Fluent 2024 R1 to support cutwater clearance and wear ring specification selection before tooling freeze, and to confirm contract head at BEP within 3% and screen cavitation margin (NPSHr ≤ 4.0 m at 3% head-drop criterion). Validation against factory loop measurements at three repeat runs. Results required before week 38 build.</t>
+          <t>RANS CFD (ANSYS Fluent 2024 R1, SST k–omega, MRF/sliding-mesh) used to predict the performance map (flow range 0.3–1.3×Qdes), shaft torque, best efficiency point, volute tongue pressure pulsation, and cavitation margin (NPSHr based on 3% head drop) for a 250 mm end-suction centrifugal pump handling water at 25 °C. Results support cutwater clearance and wear-ring specification decisions before tooling freeze, and contract verification of head at BEP within 3%.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1447,9 +1452,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2045,7 +2050,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>BEP Head Agreement ≤ 3% and NPSHr ≤ 4.0 m</t>
+          <t>Performance Acceptance Targets</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2055,7 +2060,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>CFD predictions must match factory-loop measured head within ±3% at BEP, torque within ±4% at BEP, NPSHr within ±0.5 m of test at 3% head-drop criterion, and tongue pulsation within 30% of probe rms at 0.9–1.1×Qdes. These thresholds gate tooling freeze and contract compliance decisions.</t>
+          <t>CFD predictions must agree with factory loop test data within ±3% head at BEP, ±5% head elsewhere, ±4% torque at BEP, ±0.5 m NPSHr, and tongue pulsation within 30% of probe rms at 0.9–1.1×Qdes; NPSHr at 3% head drop must not exceed 4.0 m flag threshold.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2072,18 +2077,18 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Off-Design Head Agreement ≤ 5%</t>
+          <t>RANS CFD Performance Model</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Head predictions must fall within ±5% of test data outside the 0.8–1.1×Qdes range (revised from the initial ±2% across-map target after dry-run comparison). Low-flow behavior informs motor sizing risk and warranty exposure.</t>
+          <t>ANSYS Fluent 2024 R1 pressure-based solver with SST k–omega turbulence, MRF (frozen rotor) for map sweep and transient sliding-mesh for pulsation at two operating points; 12.9 M cell medium poly-hexcore mesh used for production.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2097,13 +2102,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2024 R1 RANS CFD Model</t>
+          <t>NPSHr Inference Model</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Pressure-based coupled solver, SST k-omega with low-Re correction (primary), poly-hexcore/structured mesh (7.4 M–25.6 M cells), MRF for performance map and transient sliding-mesh for two operating points. Cavitation model disabled in production runs; NPSHr inferred from single-phase sigma-sweep extrapolation.</t>
+          <t>Single-phase sigma-sweep proxy used to infer NPSHr by extrapolating loss trend to 3% head drop; ZGB cavitation model was planned but disabled due to convergence stalls.</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2117,13 +2122,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Factory Loop Validation Data</t>
+          <t>Factory Loop Measurements</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Three repeat runs on factory hydraulic loop at 1746–1752 rpm; calibrated magnetic flowmeter (±0.5%), differential head cell (±0.25% FS), torque meter (±0.2% FS); water at 24–27 °C. Provides Q-H, torque, and tongue rms pressure reference data for validation comparison.</t>
+          <t>Three-repeat test campaign on factory hydraulic loop with calibrated magnetic flowmeter (±0.5%), differential head cell (±0.25% FS), and torque meter (±0.2% FS) at 1746–1752 rpm; water at 24–27 °C.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2137,13 +2142,13 @@
       </c>
       <c r="B7" s="41" t="inlineStr">
         <is>
-          <t>GitLab Repo PUMP250_CFD v1.7</t>
+          <t>UQ Latin Hypercube Sample Set</t>
         </is>
       </c>
       <c r="C7" s="24" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Version-controlled repository containing all CFD case setups, meshes, and post-processing scripts. Partial scripting gap noted: Slide 10 overlay post-processing used manual Excel/CSV workflow.</t>
+          <t>30-sample LHS surrogate-based uncertainty propagation covering flowmeter bias, head cell bias, rpm, water temperature, tip gap, and wear ring clearance; surrogate trained on four MRF points and one SM point.</t>
         </is>
       </c>
       <c r="E7" s="33" t="n"/>
@@ -2285,7 +2290,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>BEP Head and Torque Comparison to Factory Loop</t>
+          <t>BEP Head and Torque Comparison</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2300,12 +2305,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Medium-grid SST CFD head at BEP (1.02×Qdes, 1750 rpm) compared to three factory-loop repeats. Head error +0.5%, torque error +1.2% at BEP.</t>
+          <t>CFD head at BEP (1.02×Qdes, medium grid, SST) compared to factory loop mean of three repeats; torque also compared.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Factory loop calibrated differential head cell and torque meter; three repeat runs at 1746–1752 rpm</t>
+          <t>Factory loop calibrated measurements</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2315,12 +2320,12 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>Latin Hypercube Sampling (30 samples) on fast surrogate; 95% head interval at BEP ±1.2 m reported</t>
+          <t>Latin hypercube sampling with surrogate (30 samples); 95% head interval ±1.2 m at BEP</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>Head error +0.5% (within ±3% criterion); torque +1.2% (within ±4% criterion)</t>
+          <t>Head error +0.5% (CFD 58.4 m vs test 58.1 m); torque error +1.2%</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2332,7 +2337,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Off-Design Head Comparison (Low Flow and High Flow)</t>
+          <t>Off-Design Head Comparison (Low Flow)</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2343,12 +2348,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>CFD head compared to test at 0.6×Qdes and 1.2×Qdes. At 0.6×Qdes, CFD overpredicts head by 9–12% depending on mesh; at 1.2×Qdes, head within 4%. Tongue rms pulsation 35% below probe rms at 0.6×Qdes (outside 30% tolerance). Volute exit swirl angle underpredicted by ~6° at 1.2×Qdes.</t>
+          <t>CFD head compared to factory loop at 0.6×Qdes across coarse and medium grids.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Factory loop measured head and tongue pressure probe rms; volute exit flow angle from test</t>
+          <t>Factory loop measurements at 0.6×Qdes</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2359,7 +2364,7 @@
       <c r="G4" s="33" t="n"/>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>Low-flow head error 9–12%; tongue pulsation 35% low vs 30% criterion; swirl angle 6° underpredicted</t>
+          <t>Head overprediction 9–12% depending on mesh; exceeds ±5% acceptance band</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2371,7 +2376,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>NPSHr Estimation via Single-Phase Sigma-Sweep</t>
+          <t>Off-Design Head Comparison (High Flow)</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2382,39 +2387,35 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Cavitation model disabled due to convergence stalls. NPSHr inferred by extrapolating single-phase loss trend to 3% head drop criterion. Estimated NPSHr ~3.7 m (within ±0.5 m acceptance band of 4.0 m limit) with 95% uncertainty interval of ±0.4 m from LHS UQ. Method deviates from planned Zwart-Gerber-Belamri cavitation model; no direct cavitating-flow validation.</t>
+          <t>CFD head compared to factory loop at 1.2×Qdes; volute exit swirl angle also compared.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Contract limit of NPSHr ≤ 4.0 m; earlier ZGB pilot predicted 3.4 m (not validated)</t>
+          <t>Factory loop measurements at 1.2×Qdes</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G5" s="41" t="inlineStr">
-        <is>
-          <t>Latin Hypercube Sampling surrogate (single-phase inference, limited support points)</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" s="33" t="n"/>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>NPSHr ~3.7 m, ±0.4 m (95%); within 4.0 m limit but method fidelity unconfirmed</t>
+          <t>Head within 4% (passes ±5% band); volute exit swirl angle underpredicted by ~6°</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study (GCI, MRF, Head at BEP)</t>
+          <t>Tongue Pressure Pulsation Comparison</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2425,39 +2426,35 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Three-level grid refinement study on MRF frozen-rotor model: Coarse 7.4 M, Medium 12.9 M, Fine 25.6 M cells. Richardson extrapolated head 58.9 m; observed order ~1.9; GCI for Medium grid ~0.7% at BEP head. Tongue rms pulsation (transient SM) shows 7% gap between Medium and Fine; no GCI reported for transient cases.</t>
+          <t>Transient sliding-mesh tongue rms pressure at 1.0×Qdes compared to factory probe measurement.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolated solution</t>
+          <t>Factory loop tongue pressure probe rms</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="41" t="inlineStr">
-        <is>
-          <t>Richardson Extrapolation / Grid Convergence Index (GCI)</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>GCI ~0.7% for Medium-grid head at BEP; order ~1.9; tongue rms 7% Medium-to-Fine gap (no GCI)</t>
+          <t>CFD 35% lower than probe at 0.6×Qdes region; medium vs fine grid gap 7% (4.2 vs 4.5 kPa)</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Code Verification Spot Checks (Lid-Driven Cavity and Pipe Friction)</t>
+          <t>Mesh Convergence Study (MRF, Head at BEP)</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2468,23 +2465,27 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Internal benchmarks: lid-driven cavity (Re=1000) shows ~1.95 observed order on grid doubling 64→128→256; straight pipe SST k-omega friction factor within 2% of Blasius correlation at Re=1e5.</t>
+          <t>Richardson extrapolation applied to coarse/medium/fine grid head values at BEP to estimate discretization error.</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>Analytical/semi-empirical solutions (Blasius correlation, benchmark lid-driven cavity)</t>
+          <t>Richardson extrapolated solution (58.9 m)</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G7" s="33" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>Grid Convergence Index (Richardson extrapolation)</t>
+        </is>
+      </c>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>Order ~1.95 (cavity); friction factor error &lt;2% (pipe)</t>
+          <t>Observed order ~1.9; GCI medium ~0.7%; medium head 58.4 m vs extrapolated 58.9 m</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -2708,12 +2709,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA process and version control; peer review completed and signed</t>
+          <t>Commercial solver with documented QA processes; peer review completed and dispositioned.</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2024 R1 is a widely used commercial solver with vendor-claimed formal second-order accuracy. All case files are version-controlled in GitLab (PUMP250_CFD tag v1.7). However, parallel reduction reproducibility was not independently audited. The team QA checklist shows "peer review completed" but the calendar note confirms the review was moved to the next sprint and prior-baseline comments remain undispositioned. QA process is partially in place but peer review is incomplete.</t>
+          <t>ANSYS Fluent 2024 R1 is a well-established commercial solver with vendor-claimed formal second-order accuracy. Spot-checks (lid-driven cavity, pipe friction) were performed. However, precision and parallel reduction reproducibility were not independently audited. The team QA checklist notes "peer review completed" but the calendar shows review was moved to next sprint and prior baseline comments remain undispositioned. Postprocessing is partly manual (Excel/CSVs). Evidence is basic with notable gaps in independent QA closure.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2737,16 +2738,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Code correctly solves governing equations, demonstrated via benchmark problems or analytical solutions</t>
+          <t>Code correctly solves governing equations, demonstrated via benchmark problems or analytical comparisons.</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Two internal spot-checks are documented: (1) lid-driven cavity Re=1000 shows observed order ~1.95 on three grid levels, consistent with second-order schemes; (2) straight-pipe SST k-omega friction factor within 2% of Blasius at Re=1e5. These benchmarks are relevant to the solver's momentum and turbulence transport implementation. Vendor documentation supports second-order accuracy. Checks are limited in scope but provide adequate evidence for the physics regime of interest.</t>
+          <t>Two spot-checks performed: lid-driven cavity at Re=1000 showing ~1.95 observed order with grid doubling, and pipe friction factor within 2% of Blasius at Re=1e5 with SST k–omega. These are relevant but limited benchmarks — no MMS study, no pump-specific benchmark, and the cavitation model (ZGB) was never verified because it was disabled. Vendor documentation cited but not independently confirmed.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2774,12 +2775,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>GCI &lt; 2% for primary QoI; mesh convergence documented for both MRF and transient cases</t>
+          <t>Mesh convergence demonstrated with GCI &lt; 2% for primary QoI; transient cases also assessed.</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three-level grid refinement study performed for MRF model: Coarse 7.4 M, Medium 12.9 M, Fine 25.6 M. Richardson extrapolation yields order ~1.9; GCI for Medium-grid head at BEP ~0.7%, meeting the internal target. However, transient SM cases lack a completed GCI study — tongue rms pulsation shows a 7% Medium-to-Fine gap with no formal GCI, and two off-design points were run on the Coarse grid due to memory constraints. Discretization error is well-quantified at BEP but not across the full operating map or transient cases.</t>
+          <t>Formal three-level mesh refinement study (7.4 M / 12.9 M / 25.6 M cells) performed for MRF cases. Richardson extrapolation gives observed order ~1.9 and GCI ~0.7% for medium grid head at BEP — adequate for the primary QoI. However, two off-design points fell back to coarse grid due to memory limits. Transient pulsation mesh independence is incomplete (medium vs fine show 7% gap in tongue rms; GCI target &lt;2% not yet met). Production runs on mixed grids reduce overall confidence outside BEP.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2807,12 +2808,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Residuals below 1e-4, head monitor stable &lt;0.1%, torque oscillation &lt;0.3% rms throughout production runs</t>
+          <t>Residuals meet targets; convergence monitors stable across all production points.</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Convergence criteria are defined (residuals &lt;1e-4, head change &lt;0.1%, torque oscillation &lt;0.3% rms). However, two deviations are noted: near-shutoff points required relaxation of the residual target to 5e-4 and a switch to first-order upwind momentum for the last 500 iterations. Early documentation stated all points run second-order throughout, conflicting with the final mixed-order setup. This inconsistency reduces confidence in solver error control at off-design conditions.</t>
+          <t>Convergence criteria defined: residuals below 1e-4, head change &lt;0.1% over last 300 iterations, torque oscillation &lt;0.3% rms. For transient SM runs, 8 inner iterations per step over 3 rotor revolutions. However, near-shutoff stabilization required switching to first-order upwind and relaxing residual target to 5e-4, and early documentation incorrectly described all points as second-order. Mixed numerics across production deck introduce inconsistency. Convergence at off-design points not fully documented.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2840,12 +2841,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent peer review completed and signed; boundary conditions verified against test rig; geometry version confirmed consistent</t>
+          <t>Independent review completed; boundary conditions verified against test rig; geometry version confirmed.</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Case files are version-controlled and mesh generation is reproducible via journal files. However, several use-error indicators are present: (1) peer review not yet completed (moved to next sprint); (2) geometry version mismatch — simulations used RevC but slide package earlier referenced RevD (different wear ring clearance); (3) boundary condition type changed from planned mass-flow inlet to pressure inlet without formal re-approval; (4) post-processing partly manual (Excel/CSV), not fully scripted. These open items collectively indicate meaningful use-error risk.</t>
+          <t>GitLab repository (PUMP250_CFD tag v1.7) provides traceability for case setups, meshes, and post-scripts. However, the peer review with rotating machinery SME is incomplete (scheduled for next sprint; checklist partially signed). A significant use error is documented: simulations used RevC geometry while RevD (with 0.25 mm wear ring) was referenced in earlier slides. Boundary condition approach was changed from mass-flow inlet to pressure inlet without full reconciliation. Postprocessing partly done in unscripted Excel. Multiple open inconsistencies indicate elevated use-error risk.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2873,12 +2874,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Physics closure (turbulence model, frame treatment, cavitation model) justified and documented; known limitations stated</t>
+          <t>Governing equations and turbulence model selection justified; known limitations documented; cavitation physics represented.</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>SST k-omega with low-Re correction is a reasonable choice for turbomachinery at this Reynolds number and is documented. MRF and sliding-mesh frame treatments are justified. However, the cavitation model (ZGB) was disabled in production runs and NPSHr is inferred by extrapolation — a significant departure from planned physics that is not validated. An alternative k-epsilon model was used for some sensitivity runs on coarser grids, and near-shutoff separation behavior differs substantially between models (5% head difference). Model form uncertainty is partially quantified but cavitation physics are unmodeled.</t>
+          <t>SST k–omega with low-Re correction is an appropriate choice for rotating machinery and is applied with y+ ~1–2 on blade surfaces. MRF and sliding-mesh approaches are standard for pump CFD. Known limitations are partially documented: k–epsilon used in sensitivity study shows 5% head difference near shutoff (separation suppressed), indicating model-form sensitivity. Critically, the ZGB cavitation model was disabled and NPSHr is inferred by single-phase extrapolation — a significant model-form gap for the cavitation QoI. Roughness was effectively tuned (60 µm used despite Ra ~20 µm spec) rather than derived from physics.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2906,12 +2907,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties, geometry, boundary conditions, and operating conditions well-characterized with uncertainty; as-built geometry confirmed</t>
+          <t>Geometry from verified CAD; material properties well-characterized; boundary conditions from measurements; input uncertainties quantified.</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Water properties at 298 K are well-defined. Inlet turbulence intensity (5%) is from rig pitot measurement. Flowrate controlled to ±0.5%. Geometry uncertainty is documented (tip gap ±0.05 mm, wear ring ±0.05 mm) and sensitivity runs performed. However: (1) geometry version RevC vs RevD discrepancy is unresolved; (2) as-built roughness measurements are not yet available (60 µm was effectively tuned to improve BEP match against factory spec of Ra ~20 µm); (3) inlet boundary condition type was changed (mass-flow to pressure inlet) without confirmed propagation of measurement uncertainty from the upstream pitot tree.</t>
+          <t>CAD source identified (Pump_250_RevC, exported 2026-06-15). Inlet turbulence intensity from rig pitot tree (5%). Water properties at 298 K specified. Tip clearance built into mesh at 0.28 mm. However, RevC vs RevD geometry discrepancy is unresolved. As-built roughness and clearance measurements not yet closed. Inlet boundary switched from mass-flow to pressure specification without full justification. Temperature range in test (24–27 °C) vs model (25 °C) introduces minor but unquantified mismatch. Input uncertainties for tip gap and wear ring clearance are included in the LHS study.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2932,19 +2933,19 @@
         </is>
       </c>
       <c r="C12" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Sufficient repeats to characterize test variability; production-representative test article</t>
+          <t>Adequate test repeats; pump is production-representative; sample size justified.</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Three repeat runs were conducted on the factory hydraulic loop at 1746–1752 rpm. The test article is the production pump (250 mm impeller, Pump_250_RevC geometry). Three repeats provide basic statistical characterization of run-to-run variability. No formal sample size justification is documented, but three repeats are standard practice for factory acceptance testing and are consistent with the schedule constraints noted.</t>
+          <t>Three repeat runs conducted on the factory loop. The pump tested corresponds to the production geometry (though RevC vs RevD ambiguity affects representativeness). No explicit statistical characterization of run-to-run variability is provided beyond noting repeats at 1746–1752 rpm. Three repeats is minimal but acceptable for a hydraulic performance test where variability is typically low. No formal sample size justification documented.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2972,12 +2973,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instruments traceable to standards; measurement uncertainties documented; controlled environment</t>
+          <t>Calibrated instrumentation with stated uncertainties; controlled test environment; test standards followed.</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Calibrated instruments are documented: magnetic flowmeter ±0.5% of reading, differential head cell ±0.25% FS, torque meter ±0.2% FS. Water temperature logged (24–27 °C), barometric pressure logged. 300 mm suction bell with honeycomb straightener ensures well-conditioned inlet. RPM varied slightly (1746–1752 rpm) across runs, which is a minor uncontrolled variable but within ±0.2% of nominal. Instrument traceability to national standards is not explicitly stated but the calibrated instrument list is adequate for this application.</t>
+          <t>Factory loop equipped with calibrated magnetic flowmeter (±0.5% of reading), differential head cell (±0.25% FS), and torque meter (±0.2% FS). Water temperature logged (24–27 °C); barometric pressure logged. Suction bell with honeycomb straightener for flow conditioning. Speed varied slightly (1746–1752 rpm) across repeats. Instrument calibration is documented with quantified uncertainties. No explicit reference to ASTM/ISO test standard, but instrumentation and setup are consistent with pump test practice.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3005,12 +3006,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>CFD boundary conditions matched to test conditions with uncertainty propagation; RPM, flow rate, temperature aligned</t>
+          <t>CFD boundary conditions demonstrably match test conditions; rpm, temperature, and geometry aligned.</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>CFD run at nominal 1750 rpm vs test 1746–1752 rpm — a small but uncompensated offset. Inlet boundary condition type differs from test (pressure inlet used in CFD vs intended mass-flow matching). Flow rate agreement within ±0.5% via outlet pressure ramp. Temperature alignment is reasonable (CFD 298 K vs test 24–27 °C). The UQ surrogate is trained on mixed-numerics CFD points (first/second order, two turbulence models), which degrades the validity of propagated uncertainties. Input equivalency is partially established but notable gaps remain.</t>
+          <t>CFD run at nominal 1750 rpm vs test at 1746–1752 rpm — difference small and noted. Water temperature 298 K in CFD vs 24–27 °C in test — minor density effect unquantified. Flow rate controlled to ±0.5% at outlet. However, inlet boundary condition type differs from original plan (pressure inlet vs planned mass-flow), and upstream stabilization length from test is unknown. RevC geometry used in CFD vs potential RevD as-built creates an unresolved equivalency gap. Roughness in CFD effectively tuned rather than matched to measurement.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3038,12 +3039,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative comparison at multiple operating points; all QoIs compared with uncertainty bands; errors within acceptance criteria</t>
+          <t>Quantitative comparison across the full operating map with stated acceptance bands; uncertainty bands shown; pulsation and NPSHr compared.</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Quantitative comparison is provided at BEP (head +0.5%, torque +1.2% — both passing), at 0.6×Qdes (head 9–12% error — failing ±5% criterion), at 1.2×Qdes (head within 4% — passing). Tongue rms pulsation at 0.6×Qdes is 35% below probe measurement, failing the 30% tolerance. Swirl angle underpredicted by ~6° at 1.2×Qdes. NPSHr comparison is based on inferred single-phase extrapolation without direct cavitating-flow test data. UQ intervals are reported at BEP (±1.2 m, 95%) but the surrogate quality is compromised by mixed numerics. Overall, the comparison is thorough near BEP but fails acceptance criteria at off-design conditions.</t>
+          <t>Quantitative comparisons provided: BEP head +0.5% (passes ±3% band), torque +1.2% (passes ±4%), 1.2×Qdes head within 4% (passes ±5%). At 0.6×Qdes head overprediction is 9–12% (fails ±5% band). Tongue rms is 35% below probe (fails 30% band). NPSHr compared only via single-phase inference (±0.4 m UQ interval); no direct cavitation model comparison. 95% head UQ band at BEP is ±1.2 m. Early executive communication ("within 2% across map") was inconsistent with detailed results. Swirl angle comparison at 1.2×Qdes is qualitative. Multiple acceptance criteria failures at off-design conditions reduce overall assessment.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3071,12 +3072,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs (head, torque, NPSHr, tongue pulsation) directly address the engineering decisions and are measurable both computationally and experimentally</t>
+          <t>QoIs directly address the engineering decisions; measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>The QoIs — head, shaft torque, BEP efficiency, tongue static pressure pulsation rms, and NPSHr — directly correspond to the contract compliance requirement, motor sizing risk, cavitation warranty risk, and structural loading concern identified in the project context. All QoIs are measurable in both CFD and the factory loop. The mapping from QoI to decision (cutwater clearance, wear ring spec, motor sizing, cavitation margin) is clearly stated.</t>
+          <t>The QoIs — head, torque, BEP efficiency, tongue pressure pulsation rms, and NPSHr — directly map to the three stated decisions (cutwater clearance selection, contract head verification, cavitation margin screening). All QoIs except NPSHr (cavitation model disabled) are computed and measured experimentally. The head and torque QoIs are well-defined and directly decision-relevant. NPSHr relevance is partially compromised by the inference method substituting for direct computation.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3104,12 +3105,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, operating range, flow regime, physics) match the intended COU; gaps between validation envelope and COU envelope documented</t>
+          <t>Validation performed on same geometry, at same operating conditions, covering the full flow range including cavitation conditions.</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>The factory loop uses the same pump geometry (RevC), the same speed (1750 rpm), and water at near-ambient temperature. The validation covers the core operating range 0.6–1.2×Qdes, which spans the COU of 0.3–1.3×Qdes. However, the following gaps exist: (1) validation does not cover 0.3–0.6×Qdes (the lower extreme of the COU); (2) NPSHr validation is absent — cavitation model was disabled and no cavitating-flow test comparison is available; (3) geometry version RevC vs RevD discrepancy means the as-built COU geometry may not be the validated geometry; (4) transient sliding-mesh validation is limited to two points. These gaps are documented in Slide 12 as open items.</t>
+          <t>Validation is performed on the target pump geometry at the target speed (1750 rpm) using water — well-matched to COU. The factory loop test covers the intended operating range. However, key gaps exist: (1) cavitation testing not conducted — NPSHr validation relies on single-phase inference, not ZGB cavitation simulation compared to NPSH test; (2) low-flow validation fails acceptance bands, the region most critical for motor sizing risk; (3) geometry version ambiguity (RevC vs RevD) means validation may not represent the as-built production pump; (4) transient pulsation validated only at two flow points with incomplete mesh independence. The validation envelope does not fully cover the COU envelope for cavitation and low-flow conditions.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3198,7 +3199,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The CFD model is accepted with conditions for the near-BEP operating regime (0.8–1.1×Qdes) where head error is +0.5% and torque error is +1.2%, both within acceptance criteria, and GCI is 0.7% at BEP. The model supports the contract head compliance decision and cutwater/wear ring specification selection at BEP. Conditions: (1) Low-flow predictions (&lt; 0.8×Qdes) must not be used for decision-making without re-running with sliding-mesh and consistent second-order schemes, as head errors of 9–12% exceed the ±5% criterion; (2) NPSHr of ~3.7 m is accepted as a screening estimate only — the cavitation model must be re-enabled for at least three sigma points before NPSHr can be used as a validated design commitment; (3) the RevC vs RevD geometry discrepancy must be resolved and as-built roughness measurements obtained before tooling freeze; (4) peer review must be completed and signed before the final report is issued; (5) the UQ surrogate should be retrained on consistent second-order, single-turbulence-model runs before uncertainty intervals are reported formally.</t>
+          <t>The CFD model is accepted for the near-BEP performance decision (head within ±0.5%, torque within ±1.2%, both within acceptance bands) with the following conditions recorded: (1) Low-flow predictions (0.6×Qdes) exceed the ±5% head acceptance band by a factor of 2–2.5× and must not be used for motor sizing decisions without re-running with sliding-mesh and consistent second-order numerics. (2) NPSHr is based on single-phase inference only; the 3.7 m estimate is below the 4.0 m flag threshold but carries unquantified model-form uncertainty — the ZGB cavitation model must be re-enabled for at least three sigma points before NPSHr can be formally accepted. (3) The RevC vs RevD geometry discrepancy must be resolved and as-built clearance and roughness measurements obtained before tooling freeze decisions are finalized. (4) Peer review with rotating machinery SME must be completed and all checklist items dispositioned. (5) Tongue pulsation predictions fail the 30% acceptance band and are not accepted for production decisions. Acceptance is therefore limited to BEP and near-BEP (0.8–1.1×Qdes) head and torque for contract verification, pending closure of the open items above.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -3207,7 +3208,11 @@
         </is>
       </c>
       <c r="D3" s="22" t="n"/>
-      <c r="E3" s="22" t="n"/>
+      <c r="E3" s="39" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="24" t="n"/>
